--- a/Images/2/500StatisticalSeries.xlsx
+++ b/Images/2/500StatisticalSeries.xlsx
@@ -406,28 +406,28 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C2">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="D2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F2">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -435,28 +435,28 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>0.068</v>
+        <v>0.046</v>
       </c>
       <c r="B3">
-        <v>0.168</v>
+        <v>0.172</v>
       </c>
       <c r="C3">
-        <v>0.3120000000000001</v>
+        <v>0.3400000000000001</v>
       </c>
       <c r="D3">
-        <v>0.2739999999999999</v>
+        <v>0.2719999999999999</v>
       </c>
       <c r="E3">
-        <v>0.116</v>
+        <v>0.118</v>
       </c>
       <c r="F3">
-        <v>0.04600000000000004</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="G3">
-        <v>0.01400000000000001</v>
+        <v>0.01200000000000001</v>
       </c>
       <c r="H3">
-        <v>0.002000000000000002</v>
+        <v>0</v>
       </c>
       <c r="I3">
         <v>0</v>

--- a/Images/2/500StatisticalSeries.xlsx
+++ b/Images/2/500StatisticalSeries.xlsx
@@ -406,25 +406,25 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="B2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C2">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="D2">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="E2">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -435,25 +435,25 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3">
-        <v>0.046</v>
+        <v>0.064</v>
       </c>
       <c r="B3">
-        <v>0.172</v>
+        <v>0.186</v>
       </c>
       <c r="C3">
-        <v>0.3400000000000001</v>
+        <v>0.3080000000000001</v>
       </c>
       <c r="D3">
-        <v>0.2719999999999999</v>
+        <v>0.242</v>
       </c>
       <c r="E3">
-        <v>0.118</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="F3">
-        <v>0.04000000000000004</v>
+        <v>0.04200000000000004</v>
       </c>
       <c r="G3">
-        <v>0.01200000000000001</v>
+        <v>0.008000000000000007</v>
       </c>
       <c r="H3">
         <v>0</v>

--- a/Images/2/500StatisticalSeries.xlsx
+++ b/Images/2/500StatisticalSeries.xlsx
@@ -47,6 +47,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="1">
     <font>
       <sz val="11"/>
@@ -64,7 +67,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -72,12 +75,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -406,59 +425,59 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="D2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E2">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F2">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3">
-        <v>0.064</v>
-      </c>
-      <c r="B3">
-        <v>0.186</v>
-      </c>
-      <c r="C3">
-        <v>0.3080000000000001</v>
-      </c>
-      <c r="D3">
-        <v>0.242</v>
-      </c>
-      <c r="E3">
-        <v>0.1499999999999999</v>
-      </c>
-      <c r="F3">
-        <v>0.04200000000000004</v>
-      </c>
-      <c r="G3">
-        <v>0.008000000000000007</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
+      <c r="A3" s="1">
+        <v>0.062</v>
+      </c>
+      <c r="B3" s="1">
+        <v>0.196</v>
+      </c>
+      <c r="C3" s="1">
+        <v>0.304</v>
+      </c>
+      <c r="D3" s="1">
+        <v>0.244</v>
+      </c>
+      <c r="E3" s="1">
+        <v>0.1339999999999999</v>
+      </c>
+      <c r="F3" s="1">
+        <v>0.04600000000000004</v>
+      </c>
+      <c r="G3" s="1">
+        <v>0.01200000000000001</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.002000000000000002</v>
+      </c>
+      <c r="I3" s="1">
         <v>0</v>
       </c>
     </row>
